--- a/public/kpi-oo-upload-template.xlsx
+++ b/public/kpi-oo-upload-template.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="60">
   <si>
     <t>메인주제</t>
   </si>
@@ -87,9 +87,6 @@
     <t>3</t>
   </si>
   <si>
-    <t>이세진</t>
-  </si>
-  <si>
     <t>문서 작성 디지털화 구축</t>
   </si>
   <si>
@@ -105,9 +102,6 @@
     <t>90% Skip</t>
   </si>
   <si>
-    <t>문승진/조재익</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -144,16 +138,9 @@
     <t>5월</t>
   </si>
   <si>
-    <t>김현빈</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">   Test PGM 연구소 / 기술팀 설비 제작</t>
   </si>
   <si>
-    <t>배준혁/김현빈</t>
-  </si>
-  <si>
     <t>AI 2 (Process혁신 및 자동화 ·고도화)</t>
   </si>
   <si>
@@ -173,10 +160,6 @@
   </si>
   <si>
     <t>8월</t>
-  </si>
-  <si>
-    <t>배준혁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>AGV 고도화</t>
@@ -201,7 +184,23 @@
     <t>50%↓</t>
   </si>
   <si>
-    <t>김준용</t>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문승진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정영석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -594,7 +593,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O7"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.44140625" bestFit="1" customWidth="1"/>
@@ -613,7 +612,7 @@
     <col min="15" max="15" width="5.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -660,7 +659,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -677,67 +676,67 @@
         <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G2" s="1">
         <v>100</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="1">
-        <v>100</v>
+        <v>27</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="1:15" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G3" s="1">
         <v>30</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J3" s="1">
         <v>100</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>20</v>
@@ -746,193 +745,194 @@
         <v>21</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G4" s="1">
         <v>100</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="1">
-        <v>100</v>
+        <v>27</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M4" s="1">
         <v>4</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="O4" s="1"/>
     </row>
-    <row r="5" spans="1:15" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G5" s="1">
         <v>100</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J5" s="1">
-        <v>100</v>
+        <v>27</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M5" s="1">
         <v>4</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="1:15" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G6" s="1">
         <v>40</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J6" s="1">
         <v>100</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="M6" s="1">
         <v>5</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O6" s="1"/>
     </row>
-    <row r="7" spans="1:15" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G7" s="1">
         <v>75</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J7" s="1">
         <v>100</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M7" s="1">
         <v>3</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O7" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="A1:O1" numberStoredAsText="1"/>
   </ignoredErrors>
